--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126146957</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126146887</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126147005</v>
       </c>
       <c r="B4" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126142745</v>
       </c>
       <c r="B5" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126145967</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126144038</v>
       </c>
       <c r="B7" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>126142745</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126144038</v>
       </c>
       <c r="B7" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126146957</v>
+        <v>126146887</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490556</v>
+        <v>490543</v>
       </c>
       <c r="R2" t="n">
-        <v>6834790</v>
+        <v>6834786</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126146887</v>
+        <v>126146957</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490543</v>
+        <v>490556</v>
       </c>
       <c r="R3" t="n">
-        <v>6834786</v>
+        <v>6834790</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>126142745</v>
       </c>
       <c r="B5" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126144038</v>
       </c>
       <c r="B7" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126146887</v>
+        <v>126146957</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490543</v>
+        <v>490556</v>
       </c>
       <c r="R2" t="n">
-        <v>6834786</v>
+        <v>6834790</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126146957</v>
+        <v>126146887</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>58025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490556</v>
+        <v>490543</v>
       </c>
       <c r="R3" t="n">
-        <v>6834790</v>
+        <v>6834786</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>126147005</v>
       </c>
       <c r="B4" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126142745</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126145967</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126144038</v>
       </c>
       <c r="B7" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126146957</v>
+        <v>126146887</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>58025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490556</v>
+        <v>490543</v>
       </c>
       <c r="R2" t="n">
-        <v>6834790</v>
+        <v>6834786</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126146887</v>
+        <v>126146957</v>
       </c>
       <c r="B3" t="n">
-        <v>58025</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490543</v>
+        <v>490556</v>
       </c>
       <c r="R3" t="n">
-        <v>6834786</v>
+        <v>6834790</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>126142745</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126144038</v>
       </c>
       <c r="B7" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126146887</v>
+        <v>126146957</v>
       </c>
       <c r="B2" t="n">
-        <v>58025</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490543</v>
+        <v>490556</v>
       </c>
       <c r="R2" t="n">
-        <v>6834786</v>
+        <v>6834790</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126146957</v>
+        <v>126146887</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490556</v>
+        <v>490543</v>
       </c>
       <c r="R3" t="n">
-        <v>6834790</v>
+        <v>6834786</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>126147005</v>
       </c>
       <c r="B4" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126142745</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126145967</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126144038</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126146957</v>
+        <v>126146887</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490556</v>
+        <v>490543</v>
       </c>
       <c r="R2" t="n">
-        <v>6834790</v>
+        <v>6834786</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126146887</v>
+        <v>126146957</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490543</v>
+        <v>490556</v>
       </c>
       <c r="R3" t="n">
-        <v>6834786</v>
+        <v>6834790</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1255,6 +1255,113 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126585823</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98265</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillhamra, skogsbilväg 2 km O om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490499</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6834978</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>sumpskog, bäck och myr</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanne Maad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanne Maad, Staffan Jansson, Anders Heggestad, lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126146887</v>
+        <v>126146957</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490543</v>
+        <v>490556</v>
       </c>
       <c r="R2" t="n">
-        <v>6834786</v>
+        <v>6834790</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126146957</v>
+        <v>126146887</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490556</v>
+        <v>490543</v>
       </c>
       <c r="R3" t="n">
-        <v>6834790</v>
+        <v>6834786</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>126585823</v>
       </c>
       <c r="B8" t="n">
-        <v>98265</v>
+        <v>98340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>126585823</v>
       </c>
       <c r="B8" t="n">
-        <v>98340</v>
+        <v>98346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24777-2025 artfynd.xlsx
+++ b/artfynd/A 24777-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johanne Maad, Staffan Jansson, Anders Heggestad, lennart karlsson</t>
+          <t>lennart karlsson, Anders Heggestad, Staffan Jansson, Johanne Maad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
